--- a/src/pandorafits/formats/nirda/level1-headers.xlsx
+++ b/src/pandorafits/formats/nirda/level1-headers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindseywiser/Desktop/Pandora/pandora-fits-main/src/pandorafits/formats/nirda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/nirda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D94512-3ACF-7F4F-ADB7-19C33A62E353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB480026-967A-B24F-B422-23B11438DA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" activeTab="1" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" activeTab="1" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Primary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -298,15 +298,6 @@
   </si>
   <si>
     <t>T</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Pandora MOC</t>
-  </si>
-  <si>
-    <t>v0.1.0</t>
   </si>
   <si>
     <t>D</t>
@@ -794,9 +785,6 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>87</v>
-      </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -805,9 +793,6 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
@@ -838,9 +823,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
@@ -849,9 +831,6 @@
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
@@ -860,9 +839,6 @@
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
@@ -871,9 +847,6 @@
       <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B15">
-        <v>226</v>
-      </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
@@ -882,9 +855,6 @@
       <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="B16">
-        <v>42</v>
-      </c>
       <c r="C16" t="s">
         <v>28</v>
       </c>
@@ -893,9 +863,6 @@
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17">
-        <v>125</v>
-      </c>
       <c r="C17" t="s">
         <v>30</v>
       </c>
@@ -904,9 +871,7 @@
       <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="2">
-        <v>153.71574452308701</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" t="s">
         <v>32</v>
       </c>
@@ -915,9 +880,7 @@
       <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="2">
-        <v>-47.156720216140499</v>
-      </c>
+      <c r="B19" s="2"/>
       <c r="C19" t="s">
         <v>34</v>
       </c>
@@ -926,9 +889,6 @@
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20">
-        <v>984</v>
-      </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -937,9 +897,6 @@
       <c r="A21" t="s">
         <v>37</v>
       </c>
-      <c r="B21">
-        <v>824</v>
-      </c>
       <c r="C21" t="s">
         <v>38</v>
       </c>
@@ -948,9 +905,6 @@
       <c r="A22" t="s">
         <v>39</v>
       </c>
-      <c r="B22">
-        <v>80</v>
-      </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -959,9 +913,6 @@
       <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="B23">
-        <v>400</v>
-      </c>
       <c r="C23" t="s">
         <v>42</v>
       </c>
@@ -970,9 +921,6 @@
       <c r="A24" t="s">
         <v>43</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
       <c r="C24" t="s">
         <v>85</v>
       </c>
@@ -981,9 +929,6 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
       <c r="C25" t="s">
         <v>84</v>
       </c>
@@ -992,9 +937,6 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
       <c r="C26" t="s">
         <v>83</v>
       </c>
@@ -1003,9 +945,6 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="B27">
-        <v>16</v>
-      </c>
       <c r="C27" t="s">
         <v>82</v>
       </c>
@@ -1014,9 +953,6 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
       <c r="C28" t="s">
         <v>81</v>
       </c>
@@ -1025,9 +961,6 @@
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
       <c r="C29" t="s">
         <v>80</v>
       </c>
@@ -1036,9 +969,6 @@
       <c r="A30" t="s">
         <v>49</v>
       </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
       <c r="C30" t="s">
         <v>79</v>
       </c>
@@ -1047,9 +977,6 @@
       <c r="A31" t="s">
         <v>50</v>
       </c>
-      <c r="B31">
-        <v>5</v>
-      </c>
       <c r="C31" t="s">
         <v>78</v>
       </c>
@@ -1058,9 +985,6 @@
       <c r="A32" t="s">
         <v>51</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
       <c r="C32" t="s">
         <v>77</v>
       </c>
@@ -1069,9 +993,6 @@
       <c r="A33" t="s">
         <v>52</v>
       </c>
-      <c r="B33">
-        <v>5</v>
-      </c>
       <c r="C33" t="s">
         <v>53</v>
       </c>
@@ -1080,9 +1001,6 @@
       <c r="A34" t="s">
         <v>54</v>
       </c>
-      <c r="B34">
-        <v>10</v>
-      </c>
       <c r="C34" t="s">
         <v>53</v>
       </c>
@@ -1091,9 +1009,7 @@
       <c r="A35" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="2">
-        <v>744941360</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" t="s">
         <v>76</v>
       </c>
@@ -1102,9 +1018,7 @@
       <c r="A36" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="2">
-        <v>792000000</v>
-      </c>
+      <c r="B36" s="2"/>
       <c r="C36" t="s">
         <v>57</v>
       </c>
@@ -1208,10 +1122,10 @@
         <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1219,10 +1133,10 @@
         <v>70</v>
       </c>
       <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1233,7 +1147,7 @@
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
